--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-06-23T05:52:59.295Z</t>
+    <t>2026-06-24T08:06:23.742Z</t>
   </si>
   <si>
     <t>Savings Accounts, Personal Loans and Credit Cards - Kotak Mahindra Bank</t>

--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-06-24T08:06:23.742Z</t>
+    <t>2026-06-24T09:22:25.269Z</t>
   </si>
   <si>
     <t>Savings Accounts, Personal Loans and Credit Cards - Kotak Mahindra Bank</t>
